--- a/shared_uploads/ontime.xlsx
+++ b/shared_uploads/ontime.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C960806\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D25727-690A-4BD8-A6C0-6270909066B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A9B4FA-D500-476F-B157-F5C88C9F8162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="129">
   <si>
     <t>Constituyentes</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Guaymallén</t>
   </si>
   <si>
-    <t>Córdoba Este</t>
-  </si>
-  <si>
     <t>Formosa</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>GM</t>
   </si>
   <si>
-    <t>3 de febrero</t>
-  </si>
-  <si>
     <t>Pilar</t>
   </si>
   <si>
@@ -182,9 +176,6 @@
     <t>Trelew</t>
   </si>
   <si>
-    <t>Hurlingham Vergara</t>
-  </si>
-  <si>
     <t>Villa Mercedes</t>
   </si>
   <si>
@@ -206,18 +197,9 @@
     <t>Tucuman Ejercito Nor.</t>
   </si>
   <si>
-    <t>Las Heras Mendoza</t>
-  </si>
-  <si>
-    <t>Maipú</t>
-  </si>
-  <si>
     <t>HC Avellaneda 2</t>
   </si>
   <si>
-    <t>Tablada</t>
-  </si>
-  <si>
     <t>Quilmes</t>
   </si>
   <si>
@@ -227,18 +209,12 @@
     <t>Alte Brown</t>
   </si>
   <si>
-    <t>Moreno</t>
-  </si>
-  <si>
     <t>José C Paz</t>
   </si>
   <si>
     <t>Paraná 2</t>
   </si>
   <si>
-    <t>Laferrere</t>
-  </si>
-  <si>
     <t>Hurlingham Villegas</t>
   </si>
   <si>
@@ -248,9 +224,6 @@
     <t>Olavarría</t>
   </si>
   <si>
-    <t>González Catán</t>
-  </si>
-  <si>
     <t>Fuerza Aérea Cba.</t>
   </si>
   <si>
@@ -272,27 +245,12 @@
     <t>Caseros</t>
   </si>
   <si>
-    <t>Donato Álvarez</t>
-  </si>
-  <si>
     <t>Posadas 2</t>
   </si>
   <si>
-    <t>Santa Rosa</t>
-  </si>
-  <si>
-    <t>Claypole</t>
-  </si>
-  <si>
     <t>General Roca</t>
   </si>
   <si>
-    <t>Morón</t>
-  </si>
-  <si>
-    <t>Moreno Derqui</t>
-  </si>
-  <si>
     <t>Otros / Canales especiales</t>
   </si>
   <si>
@@ -335,18 +293,9 @@
     <t>Full 2</t>
   </si>
   <si>
-    <t>64.0%</t>
-  </si>
-  <si>
     <t>66.7%</t>
   </si>
   <si>
-    <t>71.4%</t>
-  </si>
-  <si>
-    <t>72.7%</t>
-  </si>
-  <si>
     <t>75.0%</t>
   </si>
   <si>
@@ -359,157 +308,121 @@
     <t>Full 1</t>
   </si>
   <si>
-    <t>77.9%</t>
-  </si>
-  <si>
-    <t>79.6%</t>
-  </si>
-  <si>
     <t>Oran</t>
   </si>
   <si>
-    <t>80.8%</t>
-  </si>
-  <si>
-    <t>82.6%</t>
-  </si>
-  <si>
-    <t>83.3%</t>
-  </si>
-  <si>
-    <t>84.6%</t>
-  </si>
-  <si>
-    <t>85.0%</t>
-  </si>
-  <si>
     <t>86.7%</t>
   </si>
   <si>
-    <t>87.5%</t>
-  </si>
-  <si>
-    <t>87.8%</t>
-  </si>
-  <si>
-    <t>88.1%</t>
-  </si>
-  <si>
-    <t>88.5%</t>
-  </si>
-  <si>
-    <t>88.7%</t>
-  </si>
-  <si>
     <t>89.2%</t>
   </si>
   <si>
     <t>89.5%</t>
   </si>
   <si>
-    <t>89.6%</t>
-  </si>
-  <si>
     <t>90.0%</t>
   </si>
   <si>
-    <t>90.4%</t>
-  </si>
-  <si>
-    <t>90.7%</t>
-  </si>
-  <si>
-    <t>91.1%</t>
-  </si>
-  <si>
-    <t>91.2%</t>
-  </si>
-  <si>
-    <t>91.6%</t>
-  </si>
-  <si>
     <t>91.7%</t>
   </si>
   <si>
-    <t>91.9%</t>
-  </si>
-  <si>
-    <t>92.2%</t>
-  </si>
-  <si>
     <t>92.3%</t>
   </si>
   <si>
     <t>92.6%</t>
   </si>
   <si>
-    <t>92.8%</t>
-  </si>
-  <si>
     <t>93.4%</t>
   </si>
   <si>
-    <t>93.5%</t>
-  </si>
-  <si>
     <t>93.9%</t>
   </si>
   <si>
-    <t>95.2%</t>
-  </si>
-  <si>
     <t>Santa Fé</t>
   </si>
   <si>
-    <t>95.7%</t>
-  </si>
-  <si>
-    <t>95.8%</t>
-  </si>
-  <si>
-    <t>95.9%</t>
-  </si>
-  <si>
-    <t>96.0%</t>
-  </si>
-  <si>
-    <t>96.4%</t>
-  </si>
-  <si>
-    <t>97.0%</t>
-  </si>
-  <si>
     <t>97.1%</t>
   </si>
   <si>
     <t>Lujan</t>
   </si>
   <si>
-    <t>98.2%</t>
-  </si>
-  <si>
-    <t>99.0%</t>
-  </si>
-  <si>
     <t>99.3%</t>
   </si>
   <si>
-    <t>99.5%</t>
-  </si>
-  <si>
-    <t>99.6%</t>
-  </si>
-  <si>
     <t>100.0%</t>
   </si>
   <si>
     <t>Cordoba Sur</t>
   </si>
   <si>
-    <t>Moreno Shopping</t>
-  </si>
-  <si>
-    <t>92.5%</t>
+    <t>57.3%</t>
+  </si>
+  <si>
+    <t>70.3%</t>
+  </si>
+  <si>
+    <t>72.9%</t>
+  </si>
+  <si>
+    <t>75.4%</t>
+  </si>
+  <si>
+    <t>75.9%</t>
+  </si>
+  <si>
+    <t>80.2%</t>
+  </si>
+  <si>
+    <t>81.3%</t>
+  </si>
+  <si>
+    <t>84.7%</t>
+  </si>
+  <si>
+    <t>84.8%</t>
+  </si>
+  <si>
+    <t>85.7%</t>
+  </si>
+  <si>
+    <t>87.6%</t>
+  </si>
+  <si>
+    <t>88.9%</t>
+  </si>
+  <si>
+    <t>91.5%</t>
+  </si>
+  <si>
+    <t>92.9%</t>
+  </si>
+  <si>
+    <t>94.4%</t>
+  </si>
+  <si>
+    <t>95.5%</t>
+  </si>
+  <si>
+    <t>96.2%</t>
+  </si>
+  <si>
+    <t>96.9%</t>
+  </si>
+  <si>
+    <t>97.7%</t>
+  </si>
+  <si>
+    <t>98.0%</t>
+  </si>
+  <si>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>Mataderos</t>
+  </si>
+  <si>
+    <t>87.4%</t>
   </si>
 </sst>
 </file>
@@ -839,2392 +752,2073 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E1" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1">
-        <v>2</v>
+        <v>262</v>
       </c>
       <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C5" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C7" s="1">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
+        <v>165</v>
+      </c>
+      <c r="D7">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>343</v>
       </c>
       <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
+        <v>48</v>
+      </c>
+      <c r="E8">
+        <v>21</v>
+      </c>
+      <c r="F8">
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C9">
-        <v>12</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C10" s="1">
-        <v>4</v>
+        <v>236</v>
       </c>
       <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="E10">
+        <v>25</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>439</v>
       </c>
       <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="F11">
+        <v>36</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C12">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1">
-        <v>1136</v>
+        <v>192</v>
       </c>
       <c r="D13">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="G13">
-        <v>251</v>
+        <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C14">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="D14">
-        <v>19</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
+        <v>23</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C15">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C16">
-        <v>23</v>
+        <v>435</v>
       </c>
       <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C18">
-        <v>247</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>21</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-      <c r="F18">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C19" s="1">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="D19">
-        <v>28</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C20">
-        <v>15</v>
-      </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
+        <v>598</v>
+      </c>
+      <c r="D20">
+        <v>25</v>
+      </c>
+      <c r="E20">
+        <v>32</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C22">
-        <v>41</v>
+        <v>186</v>
       </c>
       <c r="D22">
-        <v>5</v>
-      </c>
-      <c r="E22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22">
         <v>8</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22">
         <v>8</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C23">
-        <v>682</v>
+        <v>57</v>
       </c>
       <c r="D23">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>20</v>
-      </c>
-      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23">
         <v>6</v>
       </c>
-      <c r="G23">
-        <v>81</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C24">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>7</v>
       </c>
       <c r="G24">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C25">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="D25">
-        <v>18</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C26">
-        <v>53</v>
-      </c>
-      <c r="D26">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="C27">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>7</v>
       </c>
       <c r="G27">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C28" s="1">
-        <v>1593</v>
+        <v>135</v>
       </c>
       <c r="D28">
-        <v>106</v>
-      </c>
-      <c r="E28">
-        <v>34</v>
-      </c>
-      <c r="F28">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>7</v>
       </c>
       <c r="G28">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C29">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30">
+        <v>832</v>
+      </c>
+      <c r="D30">
         <v>15</v>
       </c>
-      <c r="B30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30">
-        <v>627</v>
-      </c>
-      <c r="D30">
-        <v>56</v>
-      </c>
       <c r="E30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G30">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="1">
+        <v>66</v>
+      </c>
+      <c r="D31">
         <v>3</v>
       </c>
-      <c r="B31" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2582</v>
-      </c>
-      <c r="D31">
-        <v>118</v>
-      </c>
       <c r="E31">
-        <v>67</v>
-      </c>
-      <c r="F31">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>7</v>
       </c>
       <c r="G31">
-        <v>257</v>
+        <v>4</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C32">
-        <v>888</v>
+        <v>18</v>
       </c>
       <c r="D32">
-        <v>57</v>
-      </c>
-      <c r="E32">
-        <v>26</v>
-      </c>
-      <c r="F32">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>7</v>
       </c>
       <c r="G32">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C33">
-        <v>75</v>
-      </c>
-      <c r="D33">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C34">
-        <v>775</v>
+        <v>26</v>
       </c>
       <c r="D34">
-        <v>11</v>
-      </c>
-      <c r="E34">
-        <v>32</v>
-      </c>
-      <c r="F34">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>7</v>
       </c>
       <c r="G34">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C35">
-        <v>377</v>
+        <v>65</v>
       </c>
       <c r="D35">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>11</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C36">
-        <v>818</v>
+        <v>131</v>
       </c>
       <c r="D36">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>9</v>
-      </c>
-      <c r="F36">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>7</v>
       </c>
       <c r="G36">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C37">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>7</v>
       </c>
       <c r="G37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C38">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="D38">
-        <v>13</v>
-      </c>
-      <c r="E38">
         <v>2</v>
       </c>
-      <c r="F38">
-        <v>5</v>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>7</v>
       </c>
       <c r="G38">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C39" s="1">
-        <v>1943</v>
+        <v>50</v>
       </c>
       <c r="D39">
-        <v>71</v>
-      </c>
-      <c r="E39">
-        <v>18</v>
-      </c>
-      <c r="F39">
-        <v>68</v>
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" t="s">
+        <v>7</v>
       </c>
       <c r="G39">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C40">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="D40">
-        <v>16</v>
-      </c>
-      <c r="E40">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C41" s="1">
-        <v>13</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
+        <v>476</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C42">
-        <v>516</v>
-      </c>
-      <c r="D42">
-        <v>20</v>
-      </c>
-      <c r="E42">
-        <v>11</v>
-      </c>
-      <c r="F42">
-        <v>7</v>
-      </c>
-      <c r="G42">
-        <v>38</v>
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" t="s">
+        <v>7</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C43">
-        <v>621</v>
-      </c>
-      <c r="D43">
-        <v>14</v>
-      </c>
-      <c r="E43">
-        <v>23</v>
-      </c>
-      <c r="F43">
-        <v>8</v>
-      </c>
-      <c r="G43">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" t="s">
+        <v>7</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C44">
-        <v>423</v>
-      </c>
-      <c r="D44">
-        <v>16</v>
-      </c>
-      <c r="E44">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44">
-        <v>28</v>
+        <v>7</v>
+      </c>
+      <c r="G44" t="s">
+        <v>7</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C45">
-        <v>755</v>
-      </c>
-      <c r="D45">
-        <v>31</v>
-      </c>
-      <c r="E45">
-        <v>9</v>
-      </c>
-      <c r="F45">
-        <v>9</v>
-      </c>
-      <c r="G45">
-        <v>49</v>
+        <v>174</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" t="s">
+        <v>7</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C46" s="1">
-        <v>3319</v>
-      </c>
-      <c r="D46">
-        <v>81</v>
-      </c>
-      <c r="E46">
-        <v>41</v>
-      </c>
-      <c r="F46">
-        <v>80</v>
-      </c>
-      <c r="G46">
-        <v>202</v>
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" t="s">
+        <v>7</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="C47">
-        <v>83</v>
-      </c>
-      <c r="D47">
         <v>4</v>
       </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
       <c r="E47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="G47" t="s">
+        <v>7</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="C48">
-        <v>83</v>
-      </c>
-      <c r="D48">
         <v>2</v>
       </c>
+      <c r="D48" t="s">
+        <v>7</v>
+      </c>
       <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48">
-        <v>2</v>
-      </c>
-      <c r="G48">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="F48" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" t="s">
+        <v>7</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C49">
-        <v>978</v>
-      </c>
-      <c r="D49">
-        <v>9</v>
-      </c>
-      <c r="E49">
-        <v>26</v>
-      </c>
-      <c r="F49">
-        <v>12</v>
-      </c>
-      <c r="G49">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" t="s">
+        <v>7</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C50" s="1">
-        <v>1332</v>
-      </c>
-      <c r="D50">
-        <v>35</v>
-      </c>
-      <c r="E50">
-        <v>7</v>
-      </c>
-      <c r="F50">
-        <v>15</v>
-      </c>
-      <c r="G50">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" t="s">
+        <v>7</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C51">
-        <v>192</v>
-      </c>
-      <c r="D51">
-        <v>4</v>
-      </c>
-      <c r="E51">
-        <v>3</v>
-      </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" t="s">
+        <v>7</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="C52">
-        <v>24</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="G52" t="s">
+        <v>7</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C53" s="1">
-        <v>1730</v>
-      </c>
-      <c r="D53">
-        <v>22</v>
-      </c>
-      <c r="E53">
-        <v>34</v>
-      </c>
-      <c r="F53">
-        <v>15</v>
-      </c>
-      <c r="G53">
-        <v>71</v>
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" t="s">
+        <v>7</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C54">
-        <v>445</v>
-      </c>
-      <c r="D54">
-        <v>10</v>
-      </c>
-      <c r="E54">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
+        <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>8</v>
-      </c>
-      <c r="G54">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="G54" t="s">
+        <v>7</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C55">
-        <v>700</v>
-      </c>
-      <c r="D55">
-        <v>13</v>
-      </c>
-      <c r="E55">
-        <v>7</v>
-      </c>
-      <c r="F55">
-        <v>8</v>
-      </c>
-      <c r="G55">
-        <v>28</v>
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" t="s">
+        <v>7</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C56">
-        <v>28</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
+        <v>104</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F56" t="s">
-        <v>8</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="G56" t="s">
+        <v>7</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C57">
-        <v>855</v>
-      </c>
-      <c r="D57">
-        <v>11</v>
-      </c>
-      <c r="E57">
-        <v>10</v>
-      </c>
-      <c r="F57">
-        <v>5</v>
-      </c>
-      <c r="G57">
-        <v>26</v>
+        <v>165</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" t="s">
+        <v>7</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="C58">
-        <v>68</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58">
-        <v>1</v>
-      </c>
-      <c r="G58">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" t="s">
+        <v>7</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C59">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59">
-        <v>3</v>
-      </c>
-      <c r="G59">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" t="s">
+        <v>7</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C60">
-        <v>486</v>
-      </c>
-      <c r="D60">
-        <v>4</v>
-      </c>
-      <c r="E60">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" t="s">
+        <v>7</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
-      </c>
-      <c r="G60">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="G60" t="s">
+        <v>7</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C61">
-        <v>144</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="G61" t="s">
+        <v>7</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C62" s="1">
-        <v>1916</v>
-      </c>
-      <c r="D62">
-        <v>4</v>
-      </c>
-      <c r="E62">
-        <v>3</v>
-      </c>
-      <c r="F62">
-        <v>3</v>
-      </c>
-      <c r="G62">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" t="s">
+        <v>7</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C63">
-        <v>231</v>
+        <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F63" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" t="s">
+        <v>7</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C64">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C69">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="B75" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" t="s">
-        <v>22</v>
-      </c>
-      <c r="C78">
-        <v>1</v>
-      </c>
-      <c r="D78" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" t="s">
-        <v>8</v>
-      </c>
-      <c r="G78" t="s">
-        <v>8</v>
+        <v>73</v>
+      </c>
+      <c r="C78" s="1">
+        <v>6368</v>
+      </c>
+      <c r="D78">
+        <v>358</v>
+      </c>
+      <c r="E78">
+        <v>183</v>
+      </c>
+      <c r="F78">
+        <v>263</v>
+      </c>
+      <c r="G78">
+        <v>804</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>70</v>
-      </c>
-      <c r="B79" t="s">
-        <v>22</v>
-      </c>
-      <c r="C79">
-        <v>3</v>
-      </c>
-      <c r="D79" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
-        <v>8</v>
-      </c>
-      <c r="G79" t="s">
-        <v>8</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>154</v>
-      </c>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>71</v>
-      </c>
-      <c r="B80" t="s">
-        <v>22</v>
-      </c>
-      <c r="C80">
-        <v>3</v>
-      </c>
-      <c r="D80" t="s">
-        <v>8</v>
-      </c>
-      <c r="E80" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" t="s">
-        <v>8</v>
-      </c>
-      <c r="G80" t="s">
-        <v>8</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>72</v>
-      </c>
-      <c r="B81" t="s">
-        <v>22</v>
-      </c>
-      <c r="C81">
-        <v>3</v>
-      </c>
-      <c r="D81" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81" t="s">
-        <v>8</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>73</v>
-      </c>
-      <c r="B82" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82">
-        <v>2</v>
-      </c>
-      <c r="D82" t="s">
-        <v>8</v>
-      </c>
-      <c r="E82" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" t="s">
-        <v>8</v>
-      </c>
-      <c r="G82" t="s">
-        <v>8</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>75</v>
-      </c>
-      <c r="B83" t="s">
-        <v>22</v>
-      </c>
-      <c r="C83">
-        <v>6</v>
-      </c>
-      <c r="D83" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>76</v>
-      </c>
-      <c r="B84" t="s">
-        <v>22</v>
-      </c>
-      <c r="C84">
-        <v>1</v>
-      </c>
-      <c r="D84" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" t="s">
-        <v>8</v>
-      </c>
-      <c r="G84" t="s">
-        <v>8</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>77</v>
-      </c>
-      <c r="B85" t="s">
-        <v>22</v>
-      </c>
-      <c r="C85">
-        <v>1</v>
-      </c>
-      <c r="D85" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>8</v>
-      </c>
-      <c r="G85" t="s">
-        <v>8</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>78</v>
-      </c>
-      <c r="B86" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86">
-        <v>8</v>
-      </c>
-      <c r="D86" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" t="s">
-        <v>8</v>
-      </c>
-      <c r="G86" t="s">
-        <v>8</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>79</v>
-      </c>
-      <c r="B87" t="s">
-        <v>22</v>
-      </c>
-      <c r="C87">
-        <v>5</v>
-      </c>
-      <c r="D87" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" t="s">
-        <v>8</v>
-      </c>
-      <c r="G87" t="s">
-        <v>8</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>80</v>
-      </c>
-      <c r="B88" t="s">
-        <v>22</v>
-      </c>
-      <c r="C88">
-        <v>2</v>
-      </c>
-      <c r="D88" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" t="s">
-        <v>8</v>
-      </c>
-      <c r="G88" t="s">
-        <v>8</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>81</v>
-      </c>
-      <c r="B89" t="s">
-        <v>22</v>
-      </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>83</v>
-      </c>
-      <c r="B90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="D90" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" t="s">
-        <v>8</v>
-      </c>
-      <c r="G90" t="s">
-        <v>8</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>85</v>
-      </c>
-      <c r="B91" t="s">
-        <v>86</v>
-      </c>
-      <c r="C91">
-        <v>3</v>
-      </c>
-      <c r="D91" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>87</v>
-      </c>
-      <c r="C92" s="1">
-        <v>28607</v>
-      </c>
-      <c r="D92" s="1">
-        <v>1133</v>
-      </c>
-      <c r="E92">
-        <v>480</v>
-      </c>
-      <c r="F92">
-        <v>529</v>
-      </c>
-      <c r="G92" s="1">
-        <v>2142</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>157</v>
-      </c>
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
